--- a/data/raa/raadata_vo2maks.xlsx
+++ b/data/raa/raadata_vo2maks.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68A9358B-0DEE-4CC6-9F03-837054084087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/meretesustadlien/Documents/arbeidskrav-1/data/raa/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D4AD33-590D-BE4C-BAD8-B8A495B2C1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="19100" windowHeight="11400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rådata" sheetId="2" r:id="rId1"/>
@@ -35,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="47">
   <si>
     <t>deltager</t>
   </si>
@@ -49,9 +54,6 @@
     <t>testnummer</t>
   </si>
   <si>
-    <t>betingelse</t>
-  </si>
-  <si>
     <t>rekkefolge</t>
   </si>
   <si>
@@ -115,15 +117,9 @@
     <t>m</t>
   </si>
   <si>
-    <t>morgen</t>
-  </si>
-  <si>
     <t>MK</t>
   </si>
   <si>
-    <t>kveld</t>
-  </si>
-  <si>
     <t>P02</t>
   </si>
   <si>
@@ -179,6 +175,12 @@
   </si>
   <si>
     <t>Lasse</t>
+  </si>
+  <si>
+    <t>P07</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -188,7 +190,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,6 +202,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -212,6 +215,7 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -263,9 +267,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-tema">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013–2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -303,7 +307,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013–2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -409,7 +413,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013–2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -551,7 +555,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -560,31 +564,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06E24C91-BDC8-4C03-92F9-C9712D72874C}">
   <dimension ref="A1:AD20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="17" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="23" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="46.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="46.83203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -654,16 +658,13 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
       </c>
       <c r="C2">
         <v>23</v>
@@ -672,72 +673,69 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" s="2">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2">
         <v>46259</v>
       </c>
+      <c r="G2" s="1">
+        <v>0.375</v>
+      </c>
       <c r="H2" s="1">
-        <v>0.375</v>
+        <v>0.39166666666666666</v>
       </c>
       <c r="I2" s="1">
-        <v>0.39166666666666666</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="J2" s="1">
-        <v>0.29166666666666669</v>
+        <v>0.1</v>
       </c>
       <c r="K2" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="L2" s="1">
         <v>0.30902777777777779</v>
       </c>
-      <c r="M2">
+      <c r="L2">
         <v>87.3</v>
       </c>
-      <c r="N2" s="4">
+      <c r="M2" s="4">
         <v>61.1</v>
       </c>
-      <c r="O2" s="5">
+      <c r="N2" s="5">
         <v>5334</v>
       </c>
-      <c r="P2">
+      <c r="O2">
         <v>15</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="P2" s="1">
         <v>0.3125</v>
       </c>
+      <c r="Q2">
+        <v>209</v>
+      </c>
       <c r="R2">
-        <v>209</v>
+        <v>1.25</v>
       </c>
       <c r="S2">
-        <v>1.25</v>
+        <v>19</v>
       </c>
       <c r="T2">
-        <v>19</v>
+        <v>15.25</v>
       </c>
       <c r="U2">
-        <v>15.25</v>
+        <v>4</v>
       </c>
       <c r="V2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W2">
-        <v>7</v>
-      </c>
-      <c r="X2">
         <v>57.6</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
         <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
       </c>
       <c r="C3">
         <v>23</v>
@@ -746,72 +744,69 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="2">
+        <v>25</v>
+      </c>
+      <c r="F3" s="2">
         <v>46261</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.79166666666666663</v>
       </c>
       <c r="H3" s="1">
         <v>0.79166666666666663</v>
       </c>
       <c r="I3" s="1">
-        <v>0.79166666666666663</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="J3" s="1">
-        <v>0.29166666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="K3" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="L3" s="1">
         <v>0.30902777777777779</v>
       </c>
-      <c r="M3">
+      <c r="L3">
         <v>87.8</v>
       </c>
-      <c r="N3" s="4">
+      <c r="M3" s="4">
         <v>60.8</v>
       </c>
-      <c r="O3" s="5">
+      <c r="N3" s="5">
         <v>5342</v>
       </c>
-      <c r="P3">
+      <c r="O3">
         <v>15</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="P3" s="1">
         <v>0.3125</v>
       </c>
+      <c r="Q3">
+        <v>206</v>
+      </c>
       <c r="R3">
-        <v>206</v>
+        <v>1.29</v>
       </c>
       <c r="S3">
-        <v>1.29</v>
-      </c>
-      <c r="T3">
         <v>19</v>
       </c>
-      <c r="U3" s="3">
+      <c r="T3" s="3">
         <v>16</v>
       </c>
+      <c r="U3">
+        <v>4</v>
+      </c>
       <c r="V3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W3">
-        <v>6</v>
-      </c>
-      <c r="X3">
         <v>57.6</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>23</v>
@@ -822,70 +817,67 @@
       <c r="E4" t="s">
         <v>28</v>
       </c>
-      <c r="F4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="2">
+      <c r="F4" s="2">
         <v>46261</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.80208333333333337</v>
       </c>
       <c r="H4" s="1">
         <v>0.80208333333333337</v>
       </c>
       <c r="I4" s="1">
-        <v>0.80208333333333337</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="J4" s="1">
-        <v>0.29166666666666669</v>
+        <v>0.51041666666666663</v>
       </c>
       <c r="K4" s="1">
-        <v>0.51041666666666663</v>
-      </c>
-      <c r="L4" s="1">
         <v>0.36458333333333331</v>
       </c>
-      <c r="M4">
+      <c r="L4">
         <v>66.400000000000006</v>
       </c>
-      <c r="N4" s="4">
+      <c r="M4" s="4">
         <v>60.1</v>
       </c>
-      <c r="O4" s="5">
+      <c r="N4" s="5">
         <v>3988</v>
       </c>
-      <c r="P4">
+      <c r="O4">
         <v>13</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="P4" s="1">
         <v>0.3125</v>
       </c>
+      <c r="Q4">
+        <v>195</v>
+      </c>
       <c r="R4">
-        <v>195</v>
+        <v>1.17</v>
       </c>
       <c r="S4">
-        <v>1.17</v>
+        <v>19</v>
       </c>
       <c r="T4">
-        <v>19</v>
+        <v>9.65</v>
       </c>
       <c r="U4">
-        <v>9.65</v>
+        <v>5</v>
       </c>
       <c r="V4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>7</v>
-      </c>
-      <c r="X4">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>23</v>
@@ -894,72 +886,69 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="2">
+        <v>28</v>
+      </c>
+      <c r="F5" s="2">
         <v>46264</v>
       </c>
+      <c r="G5" s="1">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="H5" s="1">
-        <v>0.33333333333333331</v>
+        <v>0.34375</v>
       </c>
       <c r="I5" s="1">
-        <v>0.34375</v>
+        <v>0.25</v>
       </c>
       <c r="J5" s="1">
-        <v>0.25</v>
+        <v>9.375E-2</v>
       </c>
       <c r="K5" s="1">
-        <v>9.375E-2</v>
-      </c>
-      <c r="L5" s="1">
         <v>0.30902777777777779</v>
       </c>
-      <c r="M5">
+      <c r="L5">
         <v>66.400000000000006</v>
       </c>
-      <c r="N5" s="4">
+      <c r="M5" s="4">
         <v>58.3</v>
       </c>
-      <c r="O5" s="5">
+      <c r="N5" s="5">
         <v>3867</v>
       </c>
-      <c r="P5">
+      <c r="O5">
         <v>13</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="P5" s="1">
         <v>0.29166666666666669</v>
       </c>
+      <c r="Q5">
+        <v>195</v>
+      </c>
       <c r="R5">
-        <v>195</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="S5">
-        <v>1.1399999999999999</v>
+        <v>18</v>
       </c>
       <c r="T5">
-        <v>18</v>
+        <v>8.39</v>
       </c>
       <c r="U5">
-        <v>8.39</v>
+        <v>4</v>
       </c>
       <c r="V5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>6</v>
-      </c>
-      <c r="X5">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>25</v>
@@ -970,70 +959,67 @@
       <c r="E6" t="s">
         <v>28</v>
       </c>
-      <c r="F6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="2">
+      <c r="F6" s="2">
         <v>46267</v>
       </c>
+      <c r="G6" s="1">
+        <v>0.76041666666666663</v>
+      </c>
       <c r="H6" s="1">
-        <v>0.76041666666666663</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="I6" s="1">
-        <v>0.77083333333333337</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="J6" s="1">
         <v>0.35416666666666669</v>
       </c>
       <c r="K6" s="1">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="L6" s="1">
         <v>0.37152777777777779</v>
       </c>
-      <c r="M6">
+      <c r="L6">
         <v>61.7</v>
       </c>
-      <c r="N6" s="4">
+      <c r="M6" s="4">
         <v>47</v>
       </c>
+      <c r="N6">
+        <v>2902</v>
+      </c>
       <c r="O6">
-        <v>2902</v>
-      </c>
-      <c r="P6">
         <v>10</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="P6" s="1">
         <v>0.19791666666666666</v>
       </c>
-      <c r="R6">
+      <c r="Q6">
         <v>185</v>
       </c>
-      <c r="S6" s="3">
+      <c r="R6" s="3">
         <v>1.1499999999999999</v>
       </c>
+      <c r="S6">
+        <v>19</v>
+      </c>
       <c r="T6">
-        <v>19</v>
+        <v>9.92</v>
       </c>
       <c r="U6">
-        <v>9.92</v>
+        <v>4</v>
       </c>
       <c r="V6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>6</v>
-      </c>
-      <c r="X6">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>25</v>
@@ -1042,72 +1028,69 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="2">
+        <v>28</v>
+      </c>
+      <c r="F7" s="2">
         <v>46269</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.35416666666666669</v>
       </c>
       <c r="H7" s="1">
         <v>0.35416666666666669</v>
       </c>
       <c r="I7" s="1">
-        <v>0.35416666666666669</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="J7" s="1">
-        <v>0.27083333333333331</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="K7" s="1">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="L7" s="1">
         <v>0.33333333333333331</v>
       </c>
+      <c r="L7">
+        <v>62.1</v>
+      </c>
       <c r="M7">
-        <v>62.1</v>
+        <v>46.8</v>
       </c>
       <c r="N7">
-        <v>46.8</v>
+        <v>2906</v>
       </c>
       <c r="O7">
-        <v>2906</v>
-      </c>
-      <c r="P7">
         <v>10</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="P7" s="1">
         <v>0.20833333333333334</v>
       </c>
+      <c r="Q7">
+        <v>186</v>
+      </c>
       <c r="R7">
-        <v>186</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="S7">
-        <v>1.1599999999999999</v>
+        <v>19</v>
       </c>
       <c r="T7">
-        <v>19</v>
+        <v>10.119999999999999</v>
       </c>
       <c r="U7">
-        <v>10.119999999999999</v>
+        <v>5</v>
       </c>
       <c r="V7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W7">
-        <v>6</v>
-      </c>
-      <c r="X7">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8">
         <v>25</v>
@@ -1118,70 +1101,67 @@
       <c r="E8" t="s">
         <v>28</v>
       </c>
-      <c r="F8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="2">
+      <c r="F8" s="2">
         <v>46268</v>
       </c>
+      <c r="G8" s="1">
+        <v>0.77083333333333337</v>
+      </c>
       <c r="H8" s="1">
-        <v>0.77083333333333337</v>
+        <v>0.77430555555555558</v>
       </c>
       <c r="I8" s="1">
-        <v>0.77430555555555558</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="J8" s="1">
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="K8" s="1">
         <v>0.29166666666666669</v>
       </c>
-      <c r="K8" s="1">
-        <v>0.4826388888888889</v>
-      </c>
-      <c r="L8" s="1">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="M8">
+      <c r="L8">
         <v>61.7</v>
       </c>
-      <c r="N8" s="4">
+      <c r="M8" s="4">
         <v>62.1</v>
       </c>
-      <c r="O8" s="5">
+      <c r="N8" s="5">
         <v>3829.5</v>
       </c>
-      <c r="P8">
+      <c r="O8">
         <v>12</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="P8" s="1">
         <v>0.20833333333333334</v>
       </c>
+      <c r="Q8">
+        <v>201</v>
+      </c>
       <c r="R8">
-        <v>201</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="S8">
-        <v>1.1299999999999999</v>
+        <v>17</v>
       </c>
       <c r="T8">
-        <v>17</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="U8">
-        <v>8.0399999999999991</v>
+        <v>4</v>
       </c>
       <c r="V8">
         <v>4</v>
       </c>
       <c r="W8">
-        <v>4</v>
-      </c>
-      <c r="X8">
         <v>38.299999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9">
         <v>25</v>
@@ -1190,63 +1170,60 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="2">
+        <v>28</v>
+      </c>
+      <c r="F9" s="2">
         <v>46270</v>
       </c>
+      <c r="G9" s="1">
+        <v>0.35416666666666669</v>
+      </c>
       <c r="H9" s="1">
-        <v>0.35416666666666669</v>
+        <v>0.37013888888888891</v>
       </c>
       <c r="I9" s="1">
-        <v>0.37013888888888891</v>
+        <v>0.30208333333333331</v>
       </c>
       <c r="J9" s="1">
-        <v>0.30208333333333331</v>
+        <v>6.805555555555555E-2</v>
       </c>
       <c r="K9" s="1">
-        <v>6.805555555555555E-2</v>
-      </c>
-      <c r="L9" s="1">
         <v>0.29166666666666669</v>
       </c>
-      <c r="M9">
+      <c r="L9">
         <v>61.7</v>
       </c>
-      <c r="N9" s="4">
+      <c r="M9" s="4">
         <v>64.900000000000006</v>
       </c>
-      <c r="O9" s="5">
+      <c r="N9" s="5">
         <v>4001.5</v>
       </c>
-      <c r="P9">
+      <c r="O9">
         <v>13</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="P9" s="1">
         <v>0.25</v>
       </c>
+      <c r="Q9">
+        <v>207</v>
+      </c>
       <c r="R9">
-        <v>207</v>
+        <v>1.17</v>
       </c>
       <c r="S9">
-        <v>1.17</v>
+        <v>19</v>
       </c>
       <c r="T9">
-        <v>19</v>
+        <v>8.64</v>
       </c>
       <c r="U9">
-        <v>8.64</v>
+        <v>5</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>6</v>
-      </c>
-      <c r="X9">
         <v>38.299999999999997</v>
       </c>
       <c r="Y9" s="8"/>
@@ -1256,12 +1233,12 @@
       <c r="AC9" s="8"/>
       <c r="AD9" s="8"/>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C10">
         <v>25</v>
@@ -1270,72 +1247,69 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="2">
+        <v>46272</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.3125</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.23958333333333334</v>
+      </c>
+      <c r="J10" s="1">
+        <v>7.2916666666666671E-2</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="L10">
+        <v>72.8</v>
+      </c>
+      <c r="M10" s="7">
+        <v>46.3</v>
+      </c>
+      <c r="N10" s="5">
+        <v>3370.5</v>
+      </c>
+      <c r="O10">
+        <v>10</v>
+      </c>
+      <c r="P10" s="1">
+        <v>0.19166666666666668</v>
+      </c>
+      <c r="Q10">
+        <v>201</v>
+      </c>
+      <c r="R10">
+        <v>1.07</v>
+      </c>
+      <c r="S10">
+        <v>18</v>
+      </c>
+      <c r="T10">
+        <v>7.02</v>
+      </c>
+      <c r="U10">
+        <v>4</v>
+      </c>
+      <c r="V10">
+        <v>6</v>
+      </c>
+      <c r="W10">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
         <v>27</v>
-      </c>
-      <c r="G10" s="2">
-        <v>46272</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0.30208333333333331</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0.3125</v>
-      </c>
-      <c r="J10" s="1">
-        <v>0.23958333333333334</v>
-      </c>
-      <c r="K10" s="1">
-        <v>7.2916666666666671E-2</v>
-      </c>
-      <c r="L10" s="1">
-        <v>0.22916666666666666</v>
-      </c>
-      <c r="M10">
-        <v>72.8</v>
-      </c>
-      <c r="N10" s="7">
-        <v>46.3</v>
-      </c>
-      <c r="O10" s="5">
-        <v>3370.5</v>
-      </c>
-      <c r="P10">
-        <v>10</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>0.19166666666666668</v>
-      </c>
-      <c r="R10">
-        <v>201</v>
-      </c>
-      <c r="S10">
-        <v>1.07</v>
-      </c>
-      <c r="T10">
-        <v>18</v>
-      </c>
-      <c r="U10">
-        <v>7.02</v>
-      </c>
-      <c r="V10">
-        <v>4</v>
-      </c>
-      <c r="W10">
-        <v>6</v>
-      </c>
-      <c r="X10">
-        <v>59.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30">
-      <c r="A11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
       </c>
       <c r="C11">
         <v>25</v>
@@ -1344,72 +1318,69 @@
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="2">
+        <v>25</v>
+      </c>
+      <c r="F11" s="2">
         <v>46274</v>
       </c>
+      <c r="G11" s="1">
+        <v>0.79166666666666663</v>
+      </c>
       <c r="H11" s="1">
-        <v>0.79166666666666663</v>
+        <v>0.80555555555555558</v>
       </c>
       <c r="I11" s="1">
-        <v>0.80555555555555558</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="J11" s="1">
-        <v>0.41666666666666669</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="K11" s="1">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="L11" s="1">
         <v>0.35416666666666669</v>
       </c>
-      <c r="M11">
+      <c r="L11">
         <v>72</v>
       </c>
-      <c r="N11" s="4">
+      <c r="M11" s="4">
         <v>46.2</v>
       </c>
-      <c r="O11" s="5">
+      <c r="N11" s="5">
         <v>3339</v>
       </c>
-      <c r="P11">
+      <c r="O11">
         <v>10</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="P11" s="1">
         <v>0.19444444444444445</v>
       </c>
+      <c r="Q11">
+        <v>202</v>
+      </c>
       <c r="R11">
-        <v>202</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="S11">
-        <v>1.1399999999999999</v>
+        <v>19</v>
       </c>
       <c r="T11">
-        <v>19</v>
+        <v>7.99</v>
       </c>
       <c r="U11">
-        <v>7.99</v>
+        <v>4</v>
       </c>
       <c r="V11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W11">
-        <v>5</v>
-      </c>
-      <c r="X11">
         <v>59.5</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12">
         <v>28</v>
@@ -1418,72 +1389,69 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="2">
+        <v>25</v>
+      </c>
+      <c r="F12" s="2">
         <v>46270</v>
       </c>
+      <c r="G12" s="1">
+        <v>0.375</v>
+      </c>
       <c r="H12" s="1">
-        <v>0.375</v>
+        <v>0.39027777777777778</v>
       </c>
       <c r="I12" s="1">
-        <v>0.39027777777777778</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="J12" s="1">
-        <v>0.27083333333333331</v>
+        <v>0.11944444444444445</v>
       </c>
       <c r="K12" s="1">
-        <v>0.11944444444444445</v>
-      </c>
-      <c r="L12" s="1">
         <v>0.25</v>
       </c>
-      <c r="M12">
+      <c r="L12">
         <v>91.7</v>
       </c>
-      <c r="N12" s="4">
+      <c r="M12" s="4">
         <v>48.1</v>
       </c>
-      <c r="O12" s="5">
+      <c r="N12" s="5">
         <v>4413.5</v>
       </c>
-      <c r="P12">
+      <c r="O12">
         <v>10</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="P12" s="1">
         <v>0.20833333333333334</v>
       </c>
+      <c r="Q12">
+        <v>188</v>
+      </c>
       <c r="R12">
-        <v>188</v>
+        <v>1.23</v>
       </c>
       <c r="S12">
-        <v>1.23</v>
+        <v>19</v>
       </c>
       <c r="T12">
-        <v>19</v>
+        <v>11.22</v>
       </c>
       <c r="U12">
-        <v>11.22</v>
+        <v>4</v>
       </c>
       <c r="V12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>6</v>
-      </c>
-      <c r="X12">
         <v>57.9</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13">
         <v>28</v>
@@ -1492,67 +1460,135 @@
         <v>2</v>
       </c>
       <c r="E13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="2">
+        <v>46272</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0.375</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L13">
+        <v>92.5</v>
+      </c>
+      <c r="M13" s="4">
+        <v>47.1</v>
+      </c>
+      <c r="N13" s="5">
+        <v>4353.5</v>
+      </c>
+      <c r="O13">
+        <v>10</v>
+      </c>
+      <c r="P13" s="1">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="Q13">
+        <v>182</v>
+      </c>
+      <c r="R13">
+        <v>1.23</v>
+      </c>
+      <c r="S13">
+        <v>19</v>
+      </c>
+      <c r="T13">
+        <v>11.58</v>
+      </c>
+      <c r="U13">
+        <v>5</v>
+      </c>
+      <c r="V13">
+        <v>7</v>
+      </c>
+      <c r="W13">
+        <v>57.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14">
+        <v>25</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
         <v>28</v>
       </c>
-      <c r="F13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" s="2">
-        <v>46272</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0.80208333333333337</v>
-      </c>
-      <c r="J13" s="1">
-        <v>0.375</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="L13" s="1">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="M13">
-        <v>92.5</v>
-      </c>
-      <c r="N13" s="4">
-        <v>47.1</v>
-      </c>
-      <c r="O13" s="5">
-        <v>4353.5</v>
-      </c>
-      <c r="P13">
-        <v>10</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="R13">
-        <v>182</v>
-      </c>
-      <c r="S13">
-        <v>1.23</v>
-      </c>
-      <c r="T13">
+      <c r="F14" s="2">
+        <v>46273</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="L14">
+        <v>84.3</v>
+      </c>
+      <c r="M14">
+        <v>48.3</v>
+      </c>
+      <c r="N14">
+        <v>4075</v>
+      </c>
+      <c r="O14">
+        <v>11</v>
+      </c>
+      <c r="P14" s="1">
+        <v>0.14583333333333334</v>
+      </c>
+      <c r="Q14">
+        <v>196</v>
+      </c>
+      <c r="R14">
+        <v>1.04</v>
+      </c>
+      <c r="S14">
         <v>19</v>
       </c>
-      <c r="U13">
-        <v>11.58</v>
-      </c>
-      <c r="V13">
+      <c r="T14">
+        <v>12.8</v>
+      </c>
+      <c r="U14">
+        <v>4</v>
+      </c>
+      <c r="V14">
         <v>5</v>
       </c>
-      <c r="W13">
-        <v>7</v>
-      </c>
-      <c r="X13">
-        <v>57.9</v>
-      </c>
-    </row>
-    <row r="19" spans="5:14">
+      <c r="W14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="5:14" x14ac:dyDescent="0.2">
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -1562,7 +1598,7 @@
       <c r="L19" s="5"/>
       <c r="N19" s="1"/>
     </row>
-    <row r="20" spans="5:14">
+    <row r="20" spans="5:14" x14ac:dyDescent="0.2">
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -1580,54 +1616,54 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C44FF029-BBFA-4132-9DE4-27C687F0A49D}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
         <v>36</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="B3" t="s">
         <v>38</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="B4" t="s">
         <v>40</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="B5" t="s">
         <v>42</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
+      <c r="B6" t="s">
         <v>44</v>
-      </c>
-      <c r="B5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
